--- a/KOPERASI JULI 26.xlsx
+++ b/KOPERASI JULI 26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2DE3FCDE-232A-417C-B8BE-D6FB3A34530D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C89497A5-FE91-4A4A-B3A1-0AE54A7E2633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="723" activeTab="3" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="723" activeTab="2" xr2:uid="{F970B87B-20DA-4A5C-AAEA-A159F2A492B1}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet 1" sheetId="37" r:id="rId1"/>
@@ -4120,8 +4120,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="42" formatCode="_(&quot;Rp&quot;* #,##0_);_(&quot;Rp&quot;* \(#,##0\);_(&quot;Rp&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="205" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-[$Rp-421]* #,##0_-;\-[$Rp-421]* #,##0_-;_-[$Rp-421]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="25" x14ac:knownFonts="1">
     <font>
@@ -4740,8 +4740,8 @@
     <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="27" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="28" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -4762,20 +4762,20 @@
   <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" xfId="30" applyFont="1"/>
-    <xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="169" fontId="5" fillId="33" borderId="1" xfId="28" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="33" borderId="1" xfId="28" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
@@ -4783,25 +4783,25 @@
     <xf numFmtId="49" fontId="2" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="36" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="205" fontId="4" fillId="36" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="4" fillId="36" borderId="0" xfId="30" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="23" fillId="37" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
@@ -20818,7 +20818,7 @@
     </row>
     <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>728</v>
+        <v>538</v>
       </c>
       <c r="B141" s="2" t="s">
         <v>197</v>
